--- a/isolated_excel/Regression - Alpha and Beta.xlsx
+++ b/isolated_excel/Regression - Alpha and Beta.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regression" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source and Method" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Regression" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Source and Method" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Regression'!$A$1:$D$3</definedName>

--- a/isolated_excel/Regression - Alpha and Beta.xlsx
+++ b/isolated_excel/Regression - Alpha and Beta.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Regression" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Source and Method" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regression" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source and Method" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Regression'!$A$1:$D$3</definedName>
@@ -443,7 +443,7 @@
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -475,13 +475,13 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3.525269540287813</v>
+        <v>3.553834897000299</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0.3947853253499741</v>
+        <v>0.3917940053800512</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>8.929586065952908</v>
+        <v>9.070671955669612</v>
       </c>
     </row>
     <row r="3">
@@ -491,13 +491,13 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>-0.02263441138176098</v>
+        <v>-0.02540694158567561</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0.0837408984724622</v>
+        <v>0.08345823680342875</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>-0.2702910023016316</v>
+        <v>-0.3044270111471107</v>
       </c>
     </row>
   </sheetData>
@@ -551,7 +551,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Jan 2017 to May 2026; 113 monthly observations</t>
+          <t>Jan 2017 to Jun 2026; 114 monthly observations</t>
         </is>
       </c>
     </row>

--- a/isolated_excel/Regression - Alpha and Beta.xlsx
+++ b/isolated_excel/Regression - Alpha and Beta.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Regression" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Source and Method" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regression" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source and Method" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Regression'!$A$1:$D$3</definedName>
@@ -443,7 +443,7 @@
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -475,13 +475,13 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3.553834897000299</v>
+        <v>3.552270603645034</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0.3917940053800512</v>
+        <v>0.3882041321353366</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>9.070671955669612</v>
+        <v>9.150522391674681</v>
       </c>
     </row>
     <row r="3">
@@ -491,13 +491,13 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>-0.02540694158567561</v>
+        <v>-0.02530998899887835</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0.08345823680342875</v>
+        <v>0.08305537019862617</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>-0.3044270111471107</v>
+        <v>-0.3047363335850498</v>
       </c>
     </row>
   </sheetData>
@@ -551,7 +551,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Jan 2017 to Jun 2026; 114 monthly observations</t>
+          <t>Jan 2017 to Jul 2026; 115 monthly observations</t>
         </is>
       </c>
     </row>

--- a/isolated_excel/Regression - Alpha and Beta.xlsx
+++ b/isolated_excel/Regression - Alpha and Beta.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regression" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source and Method" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Regression" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Source and Method" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Regression'!$A$1:$D$3</definedName>
@@ -475,13 +475,13 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3.552270603645034</v>
+        <v>3.552270603645037</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>0.3882041321353366</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>9.150522391674681</v>
+        <v>9.150522391674688</v>
       </c>
     </row>
     <row r="3">
@@ -491,13 +491,13 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>-0.02530998899887835</v>
+        <v>-0.02530998899887851</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>0.08305537019862617</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>-0.3047363335850498</v>
+        <v>-0.3047363335850518</v>
       </c>
     </row>
   </sheetData>
